--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487734_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487734_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5658</v>
+        <v>5.1681</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9282</v>
+        <v>3.4488</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6375</v>
+        <v>1.7193</v>
       </c>
       <c r="G2" t="n">
         <v>2.4143</v>
@@ -610,13 +610,13 @@
         <v>3.6866</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4067</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3667</v>
+        <v>-0.1128</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04</v>
+        <v>0.1217</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8486</v>
+        <v>4.6154</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4628</v>
+        <v>1.584</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3857</v>
+        <v>3.0314</v>
       </c>
       <c r="G3" t="n">
         <v>1.6651</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3089</v>
+        <v>0.0757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4229</v>
+        <v>-0.3017</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7317</v>
+        <v>0.3774</v>
       </c>
       <c r="V3" t="n">
         <v>1.1283</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2171</v>
+        <v>4.1192</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8242</v>
+        <v>2.3448</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3929</v>
+        <v>1.7745</v>
       </c>
       <c r="G4" t="n">
         <v>3.0397</v>
@@ -766,13 +766,13 @@
         <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.4974</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0329</v>
+        <v>0.5535</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4376</v>
+        <v>-0.0561</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7333</v>
+        <v>2.964</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9369</v>
+        <v>1.3583</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7964</v>
+        <v>1.6057</v>
       </c>
       <c r="G5" t="n">
         <v>0.0182</v>
@@ -844,13 +844,13 @@
         <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4311</v>
+        <v>-0.2005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6651</v>
+        <v>-0.2437</v>
       </c>
       <c r="U5" t="n">
-        <v>0.234</v>
+        <v>0.0432</v>
       </c>
       <c r="V5" t="n">
         <v>1.788</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>S. HERRERO GALVEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3961</v>
+        <v>-0.2869</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6802</v>
+        <v>-0.7914</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0763</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6615</v>
+        <v>-0.1596</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9592</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7024</v>
+        <v>-0.8064</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6225</v>
+        <v>0.3419</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5819</v>
+        <v>1.0092</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0406</v>
+        <v>-0.6673</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0391</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3773</v>
+        <v>-0.3625</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.139</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7645</v>
+        <v>0.0667</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6079</v>
+        <v>-0.1632</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1566</v>
+        <v>0.2299</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4004</v>
+        <v>-0.2985</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7279</v>
+        <v>-1.3203</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3275</v>
+        <v>1.0218</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5339</v>
+        <v>2.6615</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.9592</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5339</v>
+        <v>0.7024</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6673</v>
+        <v>1.6225</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.5819</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>0.0406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1335</v>
+        <v>1.0391</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3773</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1335</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.194</v>
+        <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0606</v>
+        <v>0.0698</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0606</v>
+        <v>-0.0323</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1021</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. HERRERO GALVEZ</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5477</v>
+        <v>-0.3398</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0522</v>
+        <v>-0.6673</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.3275</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1596</v>
+        <v>-0.5339</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6467000000000001</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8064</v>
+        <v>-0.5339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3419</v>
+        <v>-0.6673</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0092</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.1335</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3625</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.139</v>
+        <v>0.1335</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.424</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2299</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8712</v>
+        <v>-1.556</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0602</v>
+        <v>-1.7995</v>
       </c>
       <c r="F9" t="n">
-        <v>0.189</v>
+        <v>0.2435</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4282</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0848</v>
+        <v>0.2305</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>0.0791</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0969</v>
+        <v>0.1514</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4743</v>
+        <v>-2.189</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3224</v>
+        <v>-1.4701</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1518</v>
+        <v>-0.7189</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9473</v>
+        <v>1.4182</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2884</v>
+        <v>1.366</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2357</v>
+        <v>0.0523</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9075</v>
+        <v>1.464</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2224</v>
+        <v>1.4006</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6851</v>
+        <v>0.0634</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0398</v>
+        <v>-0.0458</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5108</v>
+        <v>-0.0346</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5506</v>
+        <v>-0.0111</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8851</v>
+        <v>-0.355</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7268</v>
+        <v>-0.0236</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1584</v>
+        <v>-0.3314</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.506</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8952</v>
+        <v>-2.2046</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.931</v>
+        <v>-2.1617</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.0428</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4182</v>
+        <v>-0.9473</v>
       </c>
       <c r="H11" t="n">
-        <v>1.366</v>
+        <v>0.2884</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0523</v>
+        <v>-1.2357</v>
       </c>
       <c r="J11" t="n">
-        <v>1.464</v>
+        <v>-0.9075</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4006</v>
+        <v>-0.2224</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0634</v>
+        <v>-0.6851</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0458</v>
+        <v>-0.0398</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0346</v>
+        <v>0.5108</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0111</v>
+        <v>-0.5506</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0612</v>
+        <v>-0.6155</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4845</v>
+        <v>-0.5661</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5767</v>
+        <v>-0.0493</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X11" t="n">
         <v>-1.506</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8438</v>
+        <v>-5.3551</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7873</v>
+        <v>-4.026</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0565</v>
+        <v>-1.3291</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9928</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3286</v>
+        <v>0.1601</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8479</v>
+        <v>-0.0867</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5193</v>
+        <v>0.2468</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.728300000000003</v>
+        <v>4.636800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4091</v>
+        <v>-3.500399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.1373</v>
+        <v>8.137400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>8.155199999999999</v>
@@ -1438,7 +1438,7 @@
         <v>12.2428</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0875</v>
+        <v>-4.087499999999999</v>
       </c>
       <c r="J13" t="n">
         <v>11.8137</v>
@@ -1447,7 +1447,7 @@
         <v>11.0071</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8067000000000002</v>
+        <v>0.8067000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-3.6585</v>
@@ -1459,7 +1459,7 @@
         <v>-4.893899999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9702000000000006</v>
+        <v>0.9701999999999997</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.4033</v>
@@ -1468,10 +1468,10 @@
         <v>20.3733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9699999999999998</v>
+        <v>-0.0618000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.806</v>
+        <v>-0.8975000000000002</v>
       </c>
       <c r="U13" t="n">
         <v>0.8356999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9021</v>
+        <v>5.2569</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4347</v>
+        <v>4.735</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4674</v>
+        <v>0.5219</v>
       </c>
       <c r="G14" t="n">
         <v>1.9486</v>
@@ -1546,13 +1546,13 @@
         <v>2.5224</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5704</v>
+        <v>-0.2156</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.775</v>
+        <v>-0.4747</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2046</v>
+        <v>0.2591</v>
       </c>
       <c r="V14" t="n">
         <v>2.1657</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5244</v>
+        <v>2.1586</v>
       </c>
       <c r="E15" t="n">
-        <v>5.698</v>
+        <v>3.4958</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1737</v>
+        <v>-1.3372</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9758</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4822</v>
+        <v>1.1165</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2289</v>
+        <v>1.0268</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2533</v>
+        <v>0.0897</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5543</v>
+        <v>2.1371</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2505</v>
+        <v>1.6509</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3039</v>
+        <v>0.4862</v>
       </c>
       <c r="G16" t="n">
         <v>3.805</v>
@@ -1702,13 +1702,13 @@
         <v>3.2985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6405</v>
+        <v>0.2232</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7627</v>
+        <v>-0.3623</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4032</v>
+        <v>0.5855</v>
       </c>
       <c r="V16" t="n">
         <v>1.6015</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3093</v>
+        <v>0.6096</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3649</v>
+        <v>0.6652</v>
       </c>
       <c r="F17" t="n">
         <v>-0.0556</v>
@@ -1780,10 +1780,10 @@
         <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2793</v>
+        <v>0.021</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U17" t="n">
         <v>0.2658</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5782</v>
+        <v>-0.1689</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7549</v>
+        <v>-0.4546</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1767</v>
+        <v>0.2857</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8696</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.3126</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1694</v>
+        <v>0.1309</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5113</v>
+        <v>-1.1203</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4411</v>
+        <v>-1.2409</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0702</v>
+        <v>0.1205</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0687</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4426</v>
+        <v>-0.0516</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1631</v>
+        <v>0.3539</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6469</v>
+        <v>-1.6196</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5696</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0501</v>
       </c>
       <c r="G20" t="n">
         <v>-1.277</v>
@@ -2014,13 +2014,13 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U20" t="n">
-        <v>0.321</v>
+        <v>0.3483</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2504</v>
+        <v>-2.023</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6299</v>
+        <v>-2.4297</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3795</v>
+        <v>0.4067</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2511</v>
@@ -2092,13 +2092,13 @@
         <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3576</v>
+        <v>-0.1301</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1683</v>
+        <v>0.0319</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1893</v>
+        <v>-0.162</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIAWARA</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4173</v>
+        <v>-2.9031</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.675</v>
+        <v>-3.2291</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2577</v>
+        <v>0.3261</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1566</v>
+        <v>-0.4743</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9402</v>
+        <v>-0.248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7835</v>
+        <v>-0.2263</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8874</v>
+        <v>0.0447</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0092</v>
+        <v>0.6715</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1218</v>
+        <v>-0.6267</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2692</v>
+        <v>-0.5191</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.931</v>
+        <v>-0.9195</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.4004</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7164</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.0448</v>
+        <v>-2.9105</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3284</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8915999999999999</v>
+        <v>-0.2064</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6931</v>
+        <v>-0.3634</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1985</v>
+        <v>0.157</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5642</v>
+        <v>-0.2821</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>M. DIAWARA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1211</v>
+        <v>-2.954</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2291</v>
+        <v>-5.0754</v>
       </c>
       <c r="F23" t="n">
-        <v>0.108</v>
+        <v>2.1214</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4743</v>
+        <v>-1.1566</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.248</v>
+        <v>-1.9402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2263</v>
+        <v>0.7835</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0447</v>
+        <v>-0.8874</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6715</v>
+        <v>-1.0092</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6267</v>
+        <v>0.1218</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5191</v>
+        <v>-0.2692</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9195</v>
+        <v>-0.931</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4004</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9403</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9105</v>
+        <v>-5.0448</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4244</v>
+        <v>0.355</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3634</v>
+        <v>0.2927</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.061</v>
+        <v>0.0623</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4931</v>
+        <v>-3.1016</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5858</v>
+        <v>-4.6849</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0927</v>
+        <v>1.5833</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2599</v>
@@ -2326,13 +2326,13 @@
         <v>3.1045</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8914</v>
+        <v>-0.4999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0655</v>
+        <v>-0.1646</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8259</v>
+        <v>-0.3353</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7282</v>
+        <v>-3.7283</v>
       </c>
       <c r="E25" t="n">
         <v>-8.1373</v>
       </c>
       <c r="F25" t="n">
-        <v>4.4091</v>
+        <v>4.4089</v>
       </c>
       <c r="G25" t="n">
         <v>-8.154999999999999</v>
@@ -2377,7 +2377,7 @@
         <v>4.0875</v>
       </c>
       <c r="J25" t="n">
-        <v>3.658400000000001</v>
+        <v>3.6584</v>
       </c>
       <c r="K25" t="n">
         <v>-1.2355</v>
@@ -2404,10 +2404,10 @@
         <v>19.4033</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9701000000000004</v>
+        <v>0.9701000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8358999999999999</v>
+        <v>-0.8358000000000002</v>
       </c>
       <c r="U25" t="n">
         <v>1.806</v>
